--- a/benchmark_output/ablation_20260602_145931/ablation_analysis.xlsx
+++ b/benchmark_output/ablation_20260602_145931/ablation_analysis.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation-Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accuracy-Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost-Ranking" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Input-Results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ground-Truth" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw-Runs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config-Definitionen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ablation-Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Accuracy-Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cost-Ranking" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Per-Input-Results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ground-Truth" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Raw-Runs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Config-Definitionen" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -439,15 +439,17 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,45 +480,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Avg Accuracy [%]</t>
+          <t>Top-1 Accuracy [%]</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Top-1 Std</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Top-1 Min</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Top-1 Max</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Top-3 Accuracy [%]</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Top-3 Std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Avg Cost/Run [USD]</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Avg Input Tokens</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>≥ Threshold</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Kosten vs P1 [%]</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Beschreibung</t>
         </is>
@@ -561,20 +573,26 @@
         <v>60</v>
       </c>
       <c r="J2" t="n">
+        <v>32</v>
+      </c>
+      <c r="K2" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.0727781</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>480767</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Keine Optimierung (Baseline)</t>
         </is>
@@ -619,20 +637,26 @@
         <v>100</v>
       </c>
       <c r="J3" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.6190870000000001</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>480767</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Keine Optimierung (Baseline)</t>
         </is>
@@ -677,20 +701,26 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.0338093</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>480762</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Keine Optimierung (Baseline)</t>
         </is>
@@ -735,20 +765,26 @@
         <v>100</v>
       </c>
       <c r="J5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.8681214</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>480762</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Keine Optimierung (Baseline)</t>
         </is>
@@ -793,20 +829,26 @@
         <v>80</v>
       </c>
       <c r="J6" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.0149104</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>96725</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>79.5</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Nur Batch-Mode</t>
         </is>
@@ -851,20 +893,26 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.1359747</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>96725</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>78</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Nur Batch-Mode</t>
         </is>
@@ -909,20 +957,26 @@
         <v>80</v>
       </c>
       <c r="J8" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.009847</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>96724</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Nur Batch-Mode</t>
         </is>
@@ -967,20 +1021,26 @@
         <v>100</v>
       </c>
       <c r="J9" t="n">
+        <v>97</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.1804415</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>96724</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>79.2</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Nur Batch-Mode</t>
         </is>
@@ -1025,20 +1085,26 @@
         <v>100</v>
       </c>
       <c r="J10" t="n">
+        <v>85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L10" t="n">
         <v>0.0008285</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>2931</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Nur Glossar-Filter</t>
         </is>
@@ -1083,20 +1149,26 @@
         <v>100</v>
       </c>
       <c r="J11" t="n">
+        <v>85</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.0162068</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>2931</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Nur Glossar-Filter</t>
         </is>
@@ -1141,20 +1213,26 @@
         <v>100</v>
       </c>
       <c r="J12" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.0072036</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>2926</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>78.7</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Nur Glossar-Filter</t>
         </is>
@@ -1199,20 +1277,26 @@
         <v>100</v>
       </c>
       <c r="J13" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.030952</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>2926</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Nur Glossar-Filter</t>
         </is>
@@ -1257,20 +1341,26 @@
         <v>40</v>
       </c>
       <c r="J14" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>22</v>
+      </c>
+      <c r="L14" t="n">
         <v>0.0726725</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>480767</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.1</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Nur Name-Priorisierung</t>
         </is>
@@ -1315,20 +1405,26 @@
         <v>100</v>
       </c>
       <c r="J15" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L15" t="n">
         <v>0.6190683</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>480767</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Nur Name-Priorisierung</t>
         </is>
@@ -1373,20 +1469,26 @@
         <v>80</v>
       </c>
       <c r="J16" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="L16" t="n">
         <v>0.033544</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>480762</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.8</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Nur Name-Priorisierung</t>
         </is>
@@ -1431,20 +1533,26 @@
         <v>80</v>
       </c>
       <c r="J17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>0.8671984</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>480762</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.1</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Nur Name-Priorisierung</t>
         </is>
@@ -1489,20 +1597,26 @@
         <v>60</v>
       </c>
       <c r="J18" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.0148813</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>96725</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Batch + Name-Priorisierung</t>
         </is>
@@ -1547,20 +1661,26 @@
         <v>100</v>
       </c>
       <c r="J19" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" t="n">
         <v>0.136202</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>96725</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>78</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Batch + Name-Priorisierung</t>
         </is>
@@ -1605,20 +1725,26 @@
         <v>80</v>
       </c>
       <c r="J20" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L20" t="n">
         <v>0.0105779</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>96724</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>68.7</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Batch + Name-Priorisierung</t>
         </is>
@@ -1663,20 +1789,26 @@
         <v>100</v>
       </c>
       <c r="J21" t="n">
+        <v>100</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>0.1802996</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>96724</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>79.2</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Batch + Name-Priorisierung</t>
         </is>
@@ -1721,20 +1853,26 @@
         <v>80</v>
       </c>
       <c r="J22" t="n">
+        <v>85</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L22" t="n">
         <v>0.0008095999999999999</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>2931</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Filter + Name-Priorisierung</t>
         </is>
@@ -1779,20 +1917,26 @@
         <v>80</v>
       </c>
       <c r="J23" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.0163422</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>2931</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Filter + Name-Priorisierung</t>
         </is>
@@ -1837,20 +1981,26 @@
         <v>80</v>
       </c>
       <c r="J24" t="n">
+        <v>89</v>
+      </c>
+      <c r="K24" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="L24" t="n">
         <v>0.0068149</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>2926</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>79.8</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Filter + Name-Priorisierung</t>
         </is>
@@ -1895,20 +2045,26 @@
         <v>80</v>
       </c>
       <c r="J25" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L25" t="n">
         <v>0.0289836</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>2926</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>96.7</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Filter + Name-Priorisierung</t>
         </is>
@@ -1953,20 +2109,26 @@
         <v>80</v>
       </c>
       <c r="J26" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" t="n">
         <v>0.0004483</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>1378</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Batch + Filter</t>
         </is>
@@ -2011,20 +2173,26 @@
         <v>100</v>
       </c>
       <c r="J27" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L27" t="n">
         <v>0.0141062</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>1378</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>97.7</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Batch + Filter</t>
         </is>
@@ -2069,20 +2237,26 @@
         <v>100</v>
       </c>
       <c r="J28" t="n">
+        <v>83</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14</v>
+      </c>
+      <c r="L28" t="n">
         <v>0.0035894</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>1377</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Batch + Filter</t>
         </is>
@@ -2127,20 +2301,26 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L29" t="n">
         <v>0.0148526</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>1377</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>98.3</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Batch + Filter</t>
         </is>
@@ -2185,20 +2365,26 @@
         <v>80</v>
       </c>
       <c r="J30" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L30" t="n">
         <v>0.000427</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>1378</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Alle Optimierungen aktiv</t>
         </is>
@@ -2243,20 +2429,26 @@
         <v>80</v>
       </c>
       <c r="J31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>0.0128429</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>1378</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Alle Optimierungen aktiv</t>
         </is>
@@ -2301,20 +2493,26 @@
         <v>80</v>
       </c>
       <c r="J32" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L32" t="n">
         <v>0.0039246</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>1377</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Alle Optimierungen aktiv</t>
         </is>
@@ -2359,20 +2557,26 @@
         <v>80</v>
       </c>
       <c r="J33" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L33" t="n">
         <v>0.0148909</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>1377</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>98.3</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Alle Optimierungen aktiv</t>
         </is>
@@ -2389,10 +2593,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2429,7 +2633,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P1_Baseline</t>
+          <t>Top-1  P1_Baseline</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2448,7 +2652,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P2_Batch</t>
+          <t>Top-1  P2_Batch</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2467,7 +2671,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P3_Filter</t>
+          <t>Top-1  P3_Filter</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2486,7 +2690,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P4_NamePref</t>
+          <t>Top-1  P4_NamePref</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2505,7 +2709,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P5_BatchName</t>
+          <t>Top-1  P5_BatchName</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2524,7 +2728,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P6_FilterName</t>
+          <t>Top-1  P6_FilterName</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2543,7 +2747,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P7_BatchFilter</t>
+          <t>Top-1  P7_BatchFilter</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2562,7 +2766,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P8_All</t>
+          <t>Top-1  P8_All</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2576,6 +2780,186 @@
       </c>
       <c r="E9" t="n">
         <v>70</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Top-3 Accuracy [%] (GT unter Top-3 Vorschlägen)</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>gpt-5-chat</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>gpt-5-nano</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>gpt-5.2-chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Top-3  P1_Baseline</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C12" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Top-3  P2_Batch</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Top-3  P3_Filter</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D14" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Top-3  P4_NamePref</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Top-3  P5_BatchName</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Top-3  P6_FilterName</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>85</v>
+      </c>
+      <c r="C17" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>89</v>
+      </c>
+      <c r="E17" t="n">
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Top-3  P7_BatchFilter</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>83</v>
+      </c>
+      <c r="E18" t="n">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Top-3  P8_All</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>98.3</v>
       </c>
     </row>
   </sheetData>
